--- a/deliverables/Export Consolidator.xlsx
+++ b/deliverables/Export Consolidator.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zakjr\Documents\Codex\2026-10-14\i-x20\outputs\export-consolidation\deliverables\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zakjr\OneDrive\Data Analytics Projects\01 Portfolio Projects\excel-export-consolidator\deliverables\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76D03556-ED5F-45FA-8617-E2FB8EF2DEE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
@@ -143,7 +143,7 @@
     <t>Folder</t>
   </si>
   <si>
-    <t>C:/Users/zakjr/Documents/Codex/2026-10-14/i-x20/outputs/export-consolidation/data/incoming</t>
+    <t>C:\Users\zakjr\OneDrive\Data Analytics Projects\01 Portfolio Projects\excel-export-consolidator\data\incoming</t>
   </si>
   <si>
     <t>2. Select Data &gt; Refresh All. Wait for all queries to finish without errors.</t>
@@ -3858,9 +3858,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="ChatGPT">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Portfolio">
   <a:themeElements>
-    <a:clrScheme name="ChatGPT">
+    <a:clrScheme name="Portfolio">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -3910,7 +3910,7 @@
         <a:cs typeface="Calibri"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="ChatGPT">
+    <a:fmtScheme name="Portfolio">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
